--- a/vehicles.xlsx
+++ b/vehicles.xlsx
@@ -486,7 +486,7 @@
       <c r="K2" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="str">
         <v>1998</v>
       </c>
       <c r="M2" t="str">
@@ -498,7 +498,7 @@
       <c r="O2">
         <v>12600</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="str">
         <v>86.625</v>
       </c>
       <c r="Q2" t="str">
@@ -539,7 +539,7 @@
       <c r="K3" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="str">
         <v>1987</v>
       </c>
       <c r="M3" t="str">
@@ -551,7 +551,7 @@
       <c r="O3">
         <v>7460</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="str">
         <v>61.975</v>
       </c>
     </row>
@@ -589,7 +589,7 @@
       <c r="K4" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="str">
         <v>2003</v>
       </c>
       <c r="M4" t="str">
@@ -601,8 +601,8 @@
       <c r="O4">
         <v>1217</v>
       </c>
-      <c r="P4">
-        <v>11.34</v>
+      <c r="P4" t="str">
+        <v>11.340</v>
       </c>
     </row>
     <row r="5">
@@ -639,7 +639,7 @@
       <c r="K5" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="str">
         <v>2006</v>
       </c>
       <c r="M5" t="str">
@@ -651,7 +651,7 @@
       <c r="O5">
         <v>1800</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="str">
         <v>21.846</v>
       </c>
     </row>
@@ -689,7 +689,7 @@
       <c r="K6" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="str">
         <v>1989</v>
       </c>
       <c r="M6" t="str">
@@ -701,8 +701,8 @@
       <c r="O6">
         <v>9880</v>
       </c>
-      <c r="P6">
-        <v>79.8</v>
+      <c r="P6" t="str">
+        <v>79.800</v>
       </c>
       <c r="Q6" t="str">
         <v>1 X USED BEDFORD MIDI - SED985700MV714618-YEAR.1994</v>
@@ -742,7 +742,7 @@
       <c r="K7" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="str">
         <v>2005</v>
       </c>
       <c r="M7" t="str">
@@ -754,8 +754,8 @@
       <c r="O7">
         <v>16700</v>
       </c>
-      <c r="P7">
-        <v>101.85</v>
+      <c r="P7" t="str">
+        <v>101.850</v>
       </c>
       <c r="Q7" t="str">
         <v>1 X USED MAN 18.232- WMAM080942M148036-YEAR 1992 1 X USED MITSUBISHI L300- JMBYZP150SA500294-YEAR 1999</v>
@@ -795,7 +795,7 @@
       <c r="K8" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="str">
         <v>1992</v>
       </c>
       <c r="M8" t="str">
@@ -807,7 +807,7 @@
       <c r="O8">
         <v>2200</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="str">
         <v>24.058</v>
       </c>
     </row>
@@ -845,7 +845,7 @@
       <c r="K9" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="str">
         <v>2002</v>
       </c>
       <c r="M9" t="str">
@@ -857,7 +857,7 @@
       <c r="O9">
         <v>6800</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="str">
         <v>62.813</v>
       </c>
     </row>
@@ -895,7 +895,7 @@
       <c r="K10" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="str">
         <v>2006</v>
       </c>
       <c r="M10" t="str">
@@ -907,7 +907,7 @@
       <c r="O10">
         <v>1387</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="str">
         <v>11.138</v>
       </c>
     </row>
@@ -945,7 +945,7 @@
       <c r="K11" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="str">
         <v>2003</v>
       </c>
       <c r="M11" t="str">
@@ -957,7 +957,7 @@
       <c r="O11">
         <v>750</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="str">
         <v>10.078</v>
       </c>
     </row>
@@ -995,7 +995,7 @@
       <c r="K12" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="str">
         <v>2011</v>
       </c>
       <c r="M12" t="str">
@@ -1007,7 +1007,7 @@
       <c r="O12">
         <v>7560</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="str">
         <v>72.188</v>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       <c r="K13" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="str">
         <v>2001</v>
       </c>
       <c r="M13" t="str">
@@ -1057,8 +1057,8 @@
       <c r="O13">
         <v>19340</v>
       </c>
-      <c r="P13">
-        <v>95.75</v>
+      <c r="P13" t="str">
+        <v>95.750</v>
       </c>
       <c r="Q13" t="str">
         <v>1 X USED CITROEN JUMPER HIGH ROOF- VF7ZCPMNC17817438-YEAR 2006</v>
@@ -1098,7 +1098,7 @@
       <c r="K14" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L14">
+      <c r="L14" t="str">
         <v>2001</v>
       </c>
       <c r="M14" t="str">
@@ -1110,7 +1110,7 @@
       <c r="O14">
         <v>2000</v>
       </c>
-      <c r="P14">
+      <c r="P14" t="str">
         <v>15.015</v>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       <c r="K15" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="str">
         <v>2015</v>
       </c>
       <c r="M15" t="str">
@@ -1160,7 +1160,7 @@
       <c r="O15">
         <v>9360</v>
       </c>
-      <c r="P15">
+      <c r="P15" t="str">
         <v>70.113</v>
       </c>
       <c r="Q15" t="str">
@@ -1201,7 +1201,7 @@
       <c r="K16" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="str">
         <v>2001</v>
       </c>
       <c r="M16" t="str">
@@ -1213,8 +1213,8 @@
       <c r="O16">
         <v>12460</v>
       </c>
-      <c r="P16">
-        <v>62</v>
+      <c r="P16" t="str">
+        <v>62.000</v>
       </c>
     </row>
     <row r="17">
@@ -1251,7 +1251,7 @@
       <c r="K17" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L17">
+      <c r="L17" t="str">
         <v>2010</v>
       </c>
       <c r="M17" t="str">
@@ -1263,7 +1263,7 @@
       <c r="O17">
         <v>1159</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="str">
         <v>10.343</v>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       <c r="K18" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L18">
+      <c r="L18" t="str">
         <v>1998</v>
       </c>
       <c r="M18" t="str">
@@ -1313,8 +1313,8 @@
       <c r="O18">
         <v>16000</v>
       </c>
-      <c r="P18">
-        <v>99</v>
+      <c r="P18" t="str">
+        <v>99.000</v>
       </c>
       <c r="Q18" t="str">
         <v>1 X USED IVECO MAGIRUS 190E42- WJMA1VSJ004195492-YEAR 1998</v>
@@ -1354,7 +1354,7 @@
       <c r="K19" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L19">
+      <c r="L19" t="str">
         <v>2000</v>
       </c>
       <c r="M19" t="str">
@@ -1366,7 +1366,7 @@
       <c r="O19">
         <v>915</v>
       </c>
-      <c r="P19">
+      <c r="P19" t="str">
         <v>9.014</v>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       <c r="K20" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="str">
         <v>2006</v>
       </c>
       <c r="M20" t="str">
@@ -1416,7 +1416,7 @@
       <c r="O20">
         <v>915</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="str">
         <v>9.014</v>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       <c r="K21" t="str">
         <v>Sarne As Consignee</v>
       </c>
-      <c r="L21">
+      <c r="L21" t="str">
         <v>2004</v>
       </c>
       <c r="M21" t="str">
@@ -1466,7 +1466,7 @@
       <c r="O21">
         <v>1270</v>
       </c>
-      <c r="P21">
+      <c r="P21" t="str">
         <v>11.201</v>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       <c r="K22" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L22">
+      <c r="L22" t="str">
         <v>2004</v>
       </c>
       <c r="M22" t="str">
@@ -1516,7 +1516,7 @@
       <c r="O22">
         <v>2530</v>
       </c>
-      <c r="P22">
+      <c r="P22" t="str">
         <v>15.749</v>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       <c r="K23" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L23">
+      <c r="L23" t="str">
         <v>2007</v>
       </c>
       <c r="M23" t="str">
@@ -1566,8 +1566,8 @@
       <c r="O23">
         <v>6100</v>
       </c>
-      <c r="P23">
-        <v>59.25</v>
+      <c r="P23" t="str">
+        <v>59.250</v>
       </c>
       <c r="Q23" t="str">
         <v>1 X USED CITROEN BERLINGO - VF77J9HN0CJ630135-YEAR 2012</v>
@@ -1607,7 +1607,7 @@
       <c r="K24" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L24">
+      <c r="L24" t="str">
         <v>1993</v>
       </c>
       <c r="M24" t="str">
@@ -1619,7 +1619,7 @@
       <c r="O24">
         <v>14640</v>
       </c>
-      <c r="P24">
+      <c r="P24" t="str">
         <v>79.999</v>
       </c>
       <c r="Q24" t="str">
@@ -1660,7 +1660,7 @@
       <c r="K25" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L25">
+      <c r="L25" t="str">
         <v>2007</v>
       </c>
       <c r="M25" t="str">
@@ -1672,7 +1672,7 @@
       <c r="O25">
         <v>1429</v>
       </c>
-      <c r="P25">
+      <c r="P25" t="str">
         <v>10.953</v>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       <c r="K26" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L26">
+      <c r="L26" t="str">
         <v>1999</v>
       </c>
       <c r="M26" t="str">
@@ -1722,7 +1722,7 @@
       <c r="O26">
         <v>26000</v>
       </c>
-      <c r="P26">
+      <c r="P26" t="str">
         <v>117.115</v>
       </c>
       <c r="Q26" t="str">
@@ -1763,7 +1763,7 @@
       <c r="K27" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L27">
+      <c r="L27" t="str">
         <v>1996</v>
       </c>
       <c r="M27" t="str">
@@ -1775,7 +1775,7 @@
       <c r="O27">
         <v>27380</v>
       </c>
-      <c r="P27">
+      <c r="P27" t="str">
         <v>174.656</v>
       </c>
       <c r="Q27" t="str">
@@ -1816,7 +1816,7 @@
       <c r="K28" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L28">
+      <c r="L28" t="str">
         <v>1985</v>
       </c>
       <c r="M28" t="str">
@@ -1828,8 +1828,8 @@
       <c r="O28">
         <v>8100</v>
       </c>
-      <c r="P28">
-        <v>58.8</v>
+      <c r="P28" t="str">
+        <v>58.800</v>
       </c>
     </row>
     <row r="29">
@@ -1866,7 +1866,7 @@
       <c r="K29" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L29">
+      <c r="L29" t="str">
         <v>2001</v>
       </c>
       <c r="M29" t="str">
@@ -1878,7 +1878,7 @@
       <c r="O29">
         <v>15540</v>
       </c>
-      <c r="P29">
+      <c r="P29" t="str">
         <v>65.488</v>
       </c>
       <c r="Q29" t="str">
@@ -1919,7 +1919,7 @@
       <c r="K30" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L30">
+      <c r="L30" t="str">
         <v>2001</v>
       </c>
       <c r="M30" t="str">
@@ -1931,8 +1931,8 @@
       <c r="O30">
         <v>9780</v>
       </c>
-      <c r="P30">
-        <v>67.65</v>
+      <c r="P30" t="str">
+        <v>67.650</v>
       </c>
       <c r="Q30" t="str">
         <v>1 X USED VOLVO FL6- YV2E4CBA938343969-YEAR 2003</v>
@@ -1972,7 +1972,7 @@
       <c r="K31" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L31">
+      <c r="L31" t="str">
         <v>2020</v>
       </c>
       <c r="M31" t="str">
@@ -1984,7 +1984,7 @@
       <c r="O31">
         <v>1150</v>
       </c>
-      <c r="P31">
+      <c r="P31" t="str">
         <v>10.785</v>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       <c r="K32" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L32">
+      <c r="L32" t="str">
         <v>2006</v>
       </c>
       <c r="M32" t="str">
@@ -2034,7 +2034,7 @@
       <c r="O32">
         <v>33040</v>
       </c>
-      <c r="P32">
+      <c r="P32" t="str">
         <v>198.494</v>
       </c>
       <c r="Q32" t="str">
@@ -2075,7 +2075,7 @@
       <c r="K33" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L33">
+      <c r="L33" t="str">
         <v>2005</v>
       </c>
       <c r="M33" t="str">
@@ -2087,7 +2087,7 @@
       <c r="O33">
         <v>1800</v>
       </c>
-      <c r="P33">
+      <c r="P33" t="str">
         <v>14.875</v>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       <c r="K34" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L34">
+      <c r="L34" t="str">
         <v>2004</v>
       </c>
       <c r="M34" t="str">
@@ -2137,8 +2137,8 @@
       <c r="O34">
         <v>750</v>
       </c>
-      <c r="P34">
-        <v>12.06</v>
+      <c r="P34" t="str">
+        <v>12.060</v>
       </c>
     </row>
     <row r="35">
@@ -2175,7 +2175,7 @@
       <c r="K35" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L35">
+      <c r="L35" t="str">
         <v>2002</v>
       </c>
       <c r="M35" t="str">
@@ -2187,8 +2187,8 @@
       <c r="O35">
         <v>8920</v>
       </c>
-      <c r="P35">
-        <v>57.75</v>
+      <c r="P35" t="str">
+        <v>57.750</v>
       </c>
     </row>
     <row r="36">
@@ -2225,7 +2225,7 @@
       <c r="K36" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L36">
+      <c r="L36" t="str">
         <v>1989</v>
       </c>
       <c r="M36" t="str">
@@ -2237,8 +2237,8 @@
       <c r="O36">
         <v>16020</v>
       </c>
-      <c r="P36">
-        <v>72.67</v>
+      <c r="P36" t="str">
+        <v>72.670</v>
       </c>
       <c r="Q36" t="str">
         <v>1 X USED MERCEDES BENZ 180 - WDD1690071J166446-YEAR 2005</v>
@@ -2278,7 +2278,7 @@
       <c r="K37" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L37">
+      <c r="L37" t="str">
         <v>2001</v>
       </c>
       <c r="M37" t="str">
@@ -2290,8 +2290,8 @@
       <c r="O37">
         <v>1780</v>
       </c>
-      <c r="P37">
-        <v>13.02</v>
+      <c r="P37" t="str">
+        <v>13.020</v>
       </c>
     </row>
     <row r="38">
@@ -2328,7 +2328,7 @@
       <c r="K38" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L38">
+      <c r="L38" t="str">
         <v>2004</v>
       </c>
       <c r="M38" t="str">
@@ -2340,8 +2340,8 @@
       <c r="O38">
         <v>750</v>
       </c>
-      <c r="P38">
-        <v>12.06</v>
+      <c r="P38" t="str">
+        <v>12.060</v>
       </c>
     </row>
     <row r="39">
@@ -2378,7 +2378,7 @@
       <c r="K39" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L39">
+      <c r="L39" t="str">
         <v>2001</v>
       </c>
       <c r="M39" t="str">
@@ -2390,7 +2390,7 @@
       <c r="O39">
         <v>18920</v>
       </c>
-      <c r="P39">
+      <c r="P39" t="str">
         <v>80.213</v>
       </c>
       <c r="Q39" t="str">
@@ -2431,7 +2431,7 @@
       <c r="K40" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L40">
+      <c r="L40" t="str">
         <v>2001</v>
       </c>
       <c r="M40" t="str">
@@ -2443,7 +2443,7 @@
       <c r="O40">
         <v>1340</v>
       </c>
-      <c r="P40">
+      <c r="P40" t="str">
         <v>12.476</v>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       <c r="K41" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L41">
+      <c r="L41" t="str">
         <v>1999</v>
       </c>
       <c r="M41" t="str">
@@ -2493,8 +2493,8 @@
       <c r="O41">
         <v>19400</v>
       </c>
-      <c r="P41">
-        <v>80.75</v>
+      <c r="P41" t="str">
+        <v>80.750</v>
       </c>
       <c r="Q41" t="str">
         <v>1 X USED MAN 26.281-</v>
@@ -2534,7 +2534,7 @@
       <c r="K42" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L42">
+      <c r="L42" t="str">
         <v>1999</v>
       </c>
       <c r="M42" t="str">
@@ -2546,8 +2546,8 @@
       <c r="O42">
         <v>22000</v>
       </c>
-      <c r="P42">
-        <v>90.85</v>
+      <c r="P42" t="str">
+        <v>90.850</v>
       </c>
       <c r="Q42" t="str">
         <v>1 X USED MAN 27.402- WMAF09F171M200682-YEAR 1995</v>
@@ -2587,7 +2587,7 @@
       <c r="K43" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L43">
+      <c r="L43" t="str">
         <v>1990</v>
       </c>
       <c r="M43" t="str">
@@ -2599,8 +2599,8 @@
       <c r="O43">
         <v>950</v>
       </c>
-      <c r="P43">
-        <v>15</v>
+      <c r="P43" t="str">
+        <v>15.000</v>
       </c>
     </row>
     <row r="44">
@@ -2637,7 +2637,7 @@
       <c r="K44" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L44">
+      <c r="L44" t="str">
         <v>1983</v>
       </c>
       <c r="M44" t="str">
@@ -2649,8 +2649,8 @@
       <c r="O44">
         <v>1800</v>
       </c>
-      <c r="P44">
-        <v>20</v>
+      <c r="P44" t="str">
+        <v>20.000</v>
       </c>
     </row>
     <row r="45">
@@ -2687,7 +2687,7 @@
       <c r="K45" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L45">
+      <c r="L45" t="str">
         <v>2000</v>
       </c>
       <c r="M45" t="str">
@@ -2699,8 +2699,8 @@
       <c r="O45">
         <v>950</v>
       </c>
-      <c r="P45">
-        <v>15</v>
+      <c r="P45" t="str">
+        <v>15.000</v>
       </c>
     </row>
     <row r="46">
@@ -2737,7 +2737,7 @@
       <c r="K46" t="str">
         <v>AFRICAN NATURAL RESOURCES AND MINES LIMITED</v>
       </c>
-      <c r="L46">
+      <c r="L46" t="str">
         <v>2025</v>
       </c>
       <c r="M46" t="str">
@@ -2749,8 +2749,8 @@
       <c r="O46">
         <v>32325</v>
       </c>
-      <c r="P46">
-        <v>139.38</v>
+      <c r="P46" t="str">
+        <v>139.380</v>
       </c>
     </row>
     <row r="47">
@@ -2787,7 +2787,7 @@
       <c r="K47" t="str">
         <v>AFRICAN NATURAL RESOURCES AND MINES LIMITED</v>
       </c>
-      <c r="L47">
+      <c r="L47" t="str">
         <v>2025</v>
       </c>
       <c r="M47" t="str">
@@ -2799,8 +2799,8 @@
       <c r="O47">
         <v>32325</v>
       </c>
-      <c r="P47">
-        <v>139.38</v>
+      <c r="P47" t="str">
+        <v>139.380</v>
       </c>
     </row>
     <row r="48">
@@ -2837,7 +2837,7 @@
       <c r="K48" t="str">
         <v>AFRICAN NATURAL RESOURCES AND MINES LIMITED</v>
       </c>
-      <c r="L48">
+      <c r="L48" t="str">
         <v>2025</v>
       </c>
       <c r="M48" t="str">
@@ -2849,8 +2849,8 @@
       <c r="O48">
         <v>32325</v>
       </c>
-      <c r="P48">
-        <v>139.38</v>
+      <c r="P48" t="str">
+        <v>139.380</v>
       </c>
     </row>
     <row r="49">
@@ -2887,7 +2887,7 @@
       <c r="K49" t="str">
         <v>AFRICAN NATURAL RESOURCES AND MINES LIMITED</v>
       </c>
-      <c r="L49">
+      <c r="L49" t="str">
         <v>2025</v>
       </c>
       <c r="M49" t="str">
@@ -2899,8 +2899,8 @@
       <c r="O49">
         <v>32325</v>
       </c>
-      <c r="P49">
-        <v>139.38</v>
+      <c r="P49" t="str">
+        <v>139.380</v>
       </c>
     </row>
     <row r="50">
@@ -2937,7 +2937,7 @@
       <c r="K50" t="str">
         <v>AFRICAN NATURAL RESOURCES AND MINES LIMITED</v>
       </c>
-      <c r="L50">
+      <c r="L50" t="str">
         <v>2025</v>
       </c>
       <c r="M50" t="str">
@@ -2949,8 +2949,8 @@
       <c r="O50">
         <v>32325</v>
       </c>
-      <c r="P50">
-        <v>139.38</v>
+      <c r="P50" t="str">
+        <v>139.380</v>
       </c>
     </row>
     <row r="51">
@@ -2987,7 +2987,7 @@
       <c r="K51" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L51">
+      <c r="L51" t="str">
         <v>1991</v>
       </c>
       <c r="M51" t="str">
@@ -2999,8 +2999,8 @@
       <c r="O51">
         <v>15620</v>
       </c>
-      <c r="P51">
-        <v>101.4</v>
+      <c r="P51" t="str">
+        <v>101.400</v>
       </c>
       <c r="Q51" t="str">
         <v>STC:Toyota Starlet CH:JT152EP9100256326 WE:808 KG YEAR:1997 STC:Mercedes Truck CH:WDB6750131K056942 WE:7000 KG YEAR:1999</v>
@@ -3040,7 +3040,7 @@
       <c r="K52" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L52">
+      <c r="L52" t="str">
         <v>2025</v>
       </c>
       <c r="M52" t="str">
@@ -3052,8 +3052,8 @@
       <c r="O52">
         <v>17600</v>
       </c>
-      <c r="P52">
-        <v>98.56</v>
+      <c r="P52" t="str">
+        <v>98.560</v>
       </c>
       <c r="Q52" t="str">
         <v>STC:MERCEDES-BENZ 1317 CH:WDB67603315909740 WE:6000 KG YEAR:1993 STC:Toyota Starlet CH:JT152EP9100289452 WE:808 KG YEAR:1997</v>
@@ -3093,7 +3093,7 @@
       <c r="K53" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L53">
+      <c r="L53" t="str">
         <v>2016</v>
       </c>
       <c r="M53" t="str">
@@ -3105,8 +3105,8 @@
       <c r="O53">
         <v>1755</v>
       </c>
-      <c r="P53">
-        <v>17.19</v>
+      <c r="P53" t="str">
+        <v>17.190</v>
       </c>
     </row>
     <row r="54">
@@ -3143,7 +3143,7 @@
       <c r="K54" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L54">
+      <c r="L54" t="str">
         <v>2006</v>
       </c>
       <c r="M54" t="str">
@@ -3155,8 +3155,8 @@
       <c r="O54">
         <v>1448</v>
       </c>
-      <c r="P54">
-        <v>12.14</v>
+      <c r="P54" t="str">
+        <v>12.140</v>
       </c>
     </row>
     <row r="55">
@@ -3193,7 +3193,7 @@
       <c r="K55" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L55">
+      <c r="L55" t="str">
         <v>1998</v>
       </c>
       <c r="M55" t="str">
@@ -3205,8 +3205,8 @@
       <c r="O55">
         <v>1284</v>
       </c>
-      <c r="P55">
-        <v>11.51</v>
+      <c r="P55" t="str">
+        <v>11.510</v>
       </c>
     </row>
     <row r="56">
@@ -3243,7 +3243,7 @@
       <c r="K56" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L56">
+      <c r="L56" t="str">
         <v>2003</v>
       </c>
       <c r="M56" t="str">
@@ -3255,8 +3255,8 @@
       <c r="O56">
         <v>1318</v>
       </c>
-      <c r="P56">
-        <v>11.18</v>
+      <c r="P56" t="str">
+        <v>11.180</v>
       </c>
     </row>
     <row r="57">
@@ -3293,7 +3293,7 @@
       <c r="K57" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L57">
+      <c r="L57" t="str">
         <v>2003</v>
       </c>
       <c r="M57" t="str">
@@ -3305,8 +3305,8 @@
       <c r="O57">
         <v>1318</v>
       </c>
-      <c r="P57">
-        <v>11.18</v>
+      <c r="P57" t="str">
+        <v>11.180</v>
       </c>
     </row>
     <row r="58">
@@ -3343,7 +3343,7 @@
       <c r="K58" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L58">
+      <c r="L58" t="str">
         <v>2008</v>
       </c>
       <c r="M58" t="str">
@@ -3355,8 +3355,8 @@
       <c r="O58">
         <v>1654</v>
       </c>
-      <c r="P58">
-        <v>16.43</v>
+      <c r="P58" t="str">
+        <v>16.430</v>
       </c>
     </row>
     <row r="59">
@@ -3393,7 +3393,7 @@
       <c r="K59" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L59">
+      <c r="L59" t="str">
         <v>2012</v>
       </c>
       <c r="M59" t="str">
@@ -3405,8 +3405,8 @@
       <c r="O59">
         <v>2200</v>
       </c>
-      <c r="P59">
-        <v>19.59</v>
+      <c r="P59" t="str">
+        <v>19.590</v>
       </c>
     </row>
     <row r="60">
@@ -3443,7 +3443,7 @@
       <c r="K60" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L60">
+      <c r="L60" t="str">
         <v>2008</v>
       </c>
       <c r="M60" t="str">
@@ -3455,8 +3455,8 @@
       <c r="O60">
         <v>1420</v>
       </c>
-      <c r="P60">
-        <v>12.77</v>
+      <c r="P60" t="str">
+        <v>12.770</v>
       </c>
     </row>
     <row r="61">
@@ -3493,7 +3493,7 @@
       <c r="K61" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L61">
+      <c r="L61" t="str">
         <v>2004</v>
       </c>
       <c r="M61" t="str">
@@ -3505,8 +3505,8 @@
       <c r="O61">
         <v>2200</v>
       </c>
-      <c r="P61">
-        <v>25.56</v>
+      <c r="P61" t="str">
+        <v>25.560</v>
       </c>
     </row>
     <row r="62">
@@ -3543,7 +3543,7 @@
       <c r="K62" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L62">
+      <c r="L62" t="str">
         <v>2003</v>
       </c>
       <c r="M62" t="str">
@@ -3555,8 +3555,8 @@
       <c r="O62">
         <v>2300</v>
       </c>
-      <c r="P62">
-        <v>22.97</v>
+      <c r="P62" t="str">
+        <v>22.970</v>
       </c>
     </row>
     <row r="63">
@@ -3593,7 +3593,7 @@
       <c r="K63" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L63">
+      <c r="L63" t="str">
         <v>1997</v>
       </c>
       <c r="M63" t="str">
@@ -3605,8 +3605,8 @@
       <c r="O63">
         <v>2200</v>
       </c>
-      <c r="P63">
-        <v>24.13</v>
+      <c r="P63" t="str">
+        <v>24.130</v>
       </c>
     </row>
     <row r="64">
@@ -3643,7 +3643,7 @@
       <c r="K64" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L64">
+      <c r="L64" t="str">
         <v>2001</v>
       </c>
       <c r="M64" t="str">
@@ -3655,8 +3655,8 @@
       <c r="O64">
         <v>1450</v>
       </c>
-      <c r="P64">
-        <v>17.59</v>
+      <c r="P64" t="str">
+        <v>17.590</v>
       </c>
     </row>
     <row r="65">
@@ -3693,7 +3693,7 @@
       <c r="K65" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L65">
+      <c r="L65" t="str">
         <v>2002</v>
       </c>
       <c r="M65" t="str">
@@ -3705,8 +3705,8 @@
       <c r="O65">
         <v>1450</v>
       </c>
-      <c r="P65">
-        <v>17.59</v>
+      <c r="P65" t="str">
+        <v>17.590</v>
       </c>
     </row>
     <row r="66">
@@ -3743,7 +3743,7 @@
       <c r="K66" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L66">
+      <c r="L66" t="str">
         <v>2002</v>
       </c>
       <c r="M66" t="str">
@@ -3755,8 +3755,8 @@
       <c r="O66">
         <v>24000</v>
       </c>
-      <c r="P66">
-        <v>110.5</v>
+      <c r="P66" t="str">
+        <v>110.500</v>
       </c>
     </row>
     <row r="67">
@@ -3793,7 +3793,7 @@
       <c r="K67" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L67">
+      <c r="L67" t="str">
         <v>2009</v>
       </c>
       <c r="M67" t="str">
@@ -3805,8 +3805,8 @@
       <c r="O67">
         <v>33000</v>
       </c>
-      <c r="P67">
-        <v>116.08</v>
+      <c r="P67" t="str">
+        <v>116.080</v>
       </c>
     </row>
     <row r="68">
@@ -3843,7 +3843,7 @@
       <c r="K68" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L68">
+      <c r="L68" t="str">
         <v>2007</v>
       </c>
       <c r="M68" t="str">
@@ -3855,8 +3855,8 @@
       <c r="O68">
         <v>1426</v>
       </c>
-      <c r="P68">
-        <v>13.4</v>
+      <c r="P68" t="str">
+        <v>13.400</v>
       </c>
     </row>
     <row r="69">
@@ -3893,7 +3893,7 @@
       <c r="K69" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L69">
+      <c r="L69" t="str">
         <v>2006</v>
       </c>
       <c r="M69" t="str">
@@ -3905,8 +3905,8 @@
       <c r="O69">
         <v>26400</v>
       </c>
-      <c r="P69">
-        <v>94.5</v>
+      <c r="P69" t="str">
+        <v>94.500</v>
       </c>
     </row>
     <row r="70">
@@ -3943,7 +3943,7 @@
       <c r="K70" t="str">
         <v>Sarne As Consignee</v>
       </c>
-      <c r="L70">
+      <c r="L70" t="str">
         <v>2016</v>
       </c>
       <c r="M70" t="str">
@@ -3955,8 +3955,8 @@
       <c r="O70">
         <v>1744</v>
       </c>
-      <c r="P70">
-        <v>13.79</v>
+      <c r="P70" t="str">
+        <v>13.790</v>
       </c>
     </row>
     <row r="71">
@@ -3993,7 +3993,7 @@
       <c r="K71" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L71">
+      <c r="L71" t="str">
         <v>2021</v>
       </c>
       <c r="M71" t="str">
@@ -4005,8 +4005,8 @@
       <c r="O71">
         <v>1720</v>
       </c>
-      <c r="P71">
-        <v>14.8</v>
+      <c r="P71" t="str">
+        <v>14.800</v>
       </c>
     </row>
     <row r="72">
@@ -4043,7 +4043,7 @@
       <c r="K72" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L72">
+      <c r="L72" t="str">
         <v>1998</v>
       </c>
       <c r="M72" t="str">
@@ -4055,8 +4055,8 @@
       <c r="O72">
         <v>4020</v>
       </c>
-      <c r="P72">
-        <v>87.21</v>
+      <c r="P72" t="str">
+        <v>87.210</v>
       </c>
       <c r="Q72" t="str">
         <v>STC:SUZUKI CARRY CH:JSAEDA21V00140717 YEAR:1993 STC:Mercedes-Benz Sprinter CH:WDB9026621R788411 YEAR:2005</v>
@@ -4096,7 +4096,7 @@
       <c r="K73" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L73">
+      <c r="L73" t="str">
         <v>2007</v>
       </c>
       <c r="M73" t="str">
@@ -4108,8 +4108,8 @@
       <c r="O73">
         <v>1445</v>
       </c>
-      <c r="P73">
-        <v>12.41</v>
+      <c r="P73" t="str">
+        <v>12.410</v>
       </c>
     </row>
     <row r="74">
@@ -4146,7 +4146,7 @@
       <c r="K74" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L74">
+      <c r="L74" t="str">
         <v>2006</v>
       </c>
       <c r="M74" t="str">
@@ -4158,8 +4158,8 @@
       <c r="O74">
         <v>1375</v>
       </c>
-      <c r="P74">
-        <v>12.5</v>
+      <c r="P74" t="str">
+        <v>12.500</v>
       </c>
     </row>
     <row r="75">
@@ -4196,7 +4196,7 @@
       <c r="K75" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L75">
+      <c r="L75" t="str">
         <v>1997</v>
       </c>
       <c r="M75" t="str">
@@ -4208,8 +4208,8 @@
       <c r="O75">
         <v>1810</v>
       </c>
-      <c r="P75">
-        <v>17.1</v>
+      <c r="P75" t="str">
+        <v>17.100</v>
       </c>
     </row>
     <row r="76">
@@ -4246,7 +4246,7 @@
       <c r="K76" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L76">
+      <c r="L76" t="str">
         <v>2017</v>
       </c>
       <c r="M76" t="str">
@@ -4258,8 +4258,8 @@
       <c r="O76">
         <v>8480</v>
       </c>
-      <c r="P76">
-        <v>59.02</v>
+      <c r="P76" t="str">
+        <v>59.020</v>
       </c>
     </row>
     <row r="77">
@@ -4296,7 +4296,7 @@
       <c r="K77" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L77">
+      <c r="L77" t="str">
         <v>2010</v>
       </c>
       <c r="M77" t="str">
@@ -4308,8 +4308,8 @@
       <c r="O77">
         <v>1830</v>
       </c>
-      <c r="P77">
-        <v>15.35</v>
+      <c r="P77" t="str">
+        <v>15.350</v>
       </c>
     </row>
     <row r="78">
@@ -4346,7 +4346,7 @@
       <c r="K78" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L78">
+      <c r="L78" t="str">
         <v>1996</v>
       </c>
       <c r="M78" t="str">
@@ -4358,8 +4358,8 @@
       <c r="O78">
         <v>4800</v>
       </c>
-      <c r="P78">
-        <v>33.95</v>
+      <c r="P78" t="str">
+        <v>33.950</v>
       </c>
       <c r="Q78" t="str">
         <v>STC:Opel Zafira A CH:W0L0TGF7532112423 YEAR:2003</v>
@@ -4399,7 +4399,7 @@
       <c r="K79" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L79">
+      <c r="L79" t="str">
         <v>1997</v>
       </c>
       <c r="M79" t="str">
@@ -4411,8 +4411,8 @@
       <c r="O79">
         <v>1580</v>
       </c>
-      <c r="P79">
-        <v>16.78</v>
+      <c r="P79" t="str">
+        <v>16.780</v>
       </c>
     </row>
     <row r="80">
@@ -4449,7 +4449,7 @@
       <c r="K80" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L80">
+      <c r="L80" t="str">
         <v>2009</v>
       </c>
       <c r="M80" t="str">
@@ -4461,8 +4461,8 @@
       <c r="O80">
         <v>17540</v>
       </c>
-      <c r="P80">
-        <v>83.95</v>
+      <c r="P80" t="str">
+        <v>83.950</v>
       </c>
     </row>
     <row r="81">
@@ -4499,7 +4499,7 @@
       <c r="K81" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L81">
+      <c r="L81" t="str">
         <v>1997</v>
       </c>
       <c r="M81" t="str">
@@ -4511,8 +4511,8 @@
       <c r="O81">
         <v>4780</v>
       </c>
-      <c r="P81">
-        <v>61.36</v>
+      <c r="P81" t="str">
+        <v>61.360</v>
       </c>
       <c r="Q81" t="str">
         <v>STC:SUZUKI CARRY CH:JSAFDA32V00143889 YEAR:2005 STC:DONGFENG MINI TRUCK CH:LGHN12179A9900563 YEAR:2011</v>
@@ -4552,7 +4552,7 @@
       <c r="K82" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L82">
+      <c r="L82" t="str">
         <v>2011</v>
       </c>
       <c r="M82" t="str">
@@ -4564,8 +4564,8 @@
       <c r="O82">
         <v>6500</v>
       </c>
-      <c r="P82">
-        <v>141.37</v>
+      <c r="P82" t="str">
+        <v>141.370</v>
       </c>
       <c r="Q82" t="str">
         <v>STC:Toyota Corolla CH:JT152EEB103166415 YEAR:1999 STC:Toyota Starlet CH-JT152EP9100478807 YEAR:1999 STC:MERCEDES-BENZ 809 CH:WDB67301215419539 YEAR:1989 STC:MERCEDES-BENZ VARIO CH:WDB67401215266886 YEAR:1986</v>
@@ -4605,7 +4605,7 @@
       <c r="K83" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L83">
+      <c r="L83" t="str">
         <v>1993</v>
       </c>
       <c r="M83" t="str">
@@ -4617,8 +4617,8 @@
       <c r="O83">
         <v>24000</v>
       </c>
-      <c r="P83">
-        <v>101.97</v>
+      <c r="P83" t="str">
+        <v>101.970</v>
       </c>
     </row>
     <row r="84">
@@ -4655,7 +4655,7 @@
       <c r="K84" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L84">
+      <c r="L84" t="str">
         <v>2007</v>
       </c>
       <c r="M84" t="str">
@@ -4667,8 +4667,8 @@
       <c r="O84">
         <v>1900</v>
       </c>
-      <c r="P84">
-        <v>13.22</v>
+      <c r="P84" t="str">
+        <v>13.220</v>
       </c>
     </row>
     <row r="85">
@@ -4705,7 +4705,7 @@
       <c r="K85" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L85">
+      <c r="L85" t="str">
         <v>2005</v>
       </c>
       <c r="M85" t="str">
@@ -4717,8 +4717,8 @@
       <c r="O85">
         <v>1724</v>
       </c>
-      <c r="P85">
-        <v>14.25</v>
+      <c r="P85" t="str">
+        <v>14.250</v>
       </c>
     </row>
     <row r="86">
@@ -4755,7 +4755,7 @@
       <c r="K86" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L86">
+      <c r="L86" t="str">
         <v>2001</v>
       </c>
       <c r="M86" t="str">
@@ -4767,8 +4767,8 @@
       <c r="O86">
         <v>1959</v>
       </c>
-      <c r="P86">
-        <v>17.06</v>
+      <c r="P86" t="str">
+        <v>17.060</v>
       </c>
     </row>
     <row r="87">
@@ -4805,7 +4805,7 @@
       <c r="K87" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L87">
+      <c r="L87" t="str">
         <v>1996</v>
       </c>
       <c r="M87" t="str">
@@ -4817,8 +4817,8 @@
       <c r="O87">
         <v>17620</v>
       </c>
-      <c r="P87">
-        <v>128.57</v>
+      <c r="P87" t="str">
+        <v>128.570</v>
       </c>
       <c r="Q87" t="str">
         <v>STC:Toyota Aygo CH:JTDKG10C80N179623 YEAR:2007 STC:MERCEDES-BENZ 408 CH:WDB9043131P752753 YEAR:1997 STC:Volkswagen Golf CH:WWWZZZ1KZ4W147634 YEAR:2004</v>
@@ -4858,7 +4858,7 @@
       <c r="K88" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L88">
+      <c r="L88" t="str">
         <v>2005</v>
       </c>
       <c r="M88" t="str">
@@ -4870,8 +4870,8 @@
       <c r="O88">
         <v>7360</v>
       </c>
-      <c r="P88">
-        <v>51.64</v>
+      <c r="P88" t="str">
+        <v>51.640</v>
       </c>
     </row>
     <row r="89">
@@ -4908,7 +4908,7 @@
       <c r="K89" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L89">
+      <c r="L89" t="str">
         <v>1997</v>
       </c>
       <c r="M89" t="str">
@@ -4920,8 +4920,8 @@
       <c r="O89">
         <v>1905</v>
       </c>
-      <c r="P89">
-        <v>14.39</v>
+      <c r="P89" t="str">
+        <v>14.390</v>
       </c>
     </row>
     <row r="90">
@@ -4958,7 +4958,7 @@
       <c r="K90" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L90">
+      <c r="L90" t="str">
         <v>1992</v>
       </c>
       <c r="M90" t="str">
@@ -4970,8 +4970,8 @@
       <c r="O90">
         <v>1645</v>
       </c>
-      <c r="P90">
-        <v>16.63</v>
+      <c r="P90" t="str">
+        <v>16.630</v>
       </c>
     </row>
     <row r="91">
@@ -5008,7 +5008,7 @@
       <c r="K91" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L91">
+      <c r="L91" t="str">
         <v>1994</v>
       </c>
       <c r="M91" t="str">
@@ -5020,8 +5020,8 @@
       <c r="O91">
         <v>1675</v>
       </c>
-      <c r="P91">
-        <v>16.63</v>
+      <c r="P91" t="str">
+        <v>16.630</v>
       </c>
     </row>
     <row r="92">
@@ -5058,7 +5058,7 @@
       <c r="K92" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L92">
+      <c r="L92" t="str">
         <v>1995</v>
       </c>
       <c r="M92" t="str">
@@ -5070,8 +5070,8 @@
       <c r="O92">
         <v>1450</v>
       </c>
-      <c r="P92">
-        <v>17.59</v>
+      <c r="P92" t="str">
+        <v>17.590</v>
       </c>
     </row>
     <row r="93">
@@ -5108,7 +5108,7 @@
       <c r="K93" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L93">
+      <c r="L93" t="str">
         <v>2007</v>
       </c>
       <c r="M93" t="str">
@@ -5120,8 +5120,8 @@
       <c r="O93">
         <v>26740</v>
       </c>
-      <c r="P93">
-        <v>169.32</v>
+      <c r="P93" t="str">
+        <v>169.320</v>
       </c>
       <c r="Q93" t="str">
         <v>STC:Nissan Micra CH:SJNEAAK11U0733801 WE:815 KG YEAR:1998 TRAILER ATTACHED CH:VW1P3EA1BSN108638 WE:9040 KG YEAR:2003 STC:MERCEDES-BENZ 814 CH:WDB67401115737633 WE:5500 KG YEAR:1998 STC:MERCEDES-BENZ 817 CH:WDB67600415917502 WE:4285 KG YEAR:1992 STC:MERCEDES-BENZ 208 CH:WDB9013121P966534 WE:1816 KG YEAR:1999</v>
@@ -5161,7 +5161,7 @@
       <c r="K94" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L94">
+      <c r="L94" t="str">
         <v>2006</v>
       </c>
       <c r="M94" t="str">
@@ -5173,8 +5173,8 @@
       <c r="O94">
         <v>29300</v>
       </c>
-      <c r="P94">
-        <v>170.15</v>
+      <c r="P94" t="str">
+        <v>170.150</v>
       </c>
       <c r="Q94" t="str">
         <v>STC:MERCEDES-BENZ 1217 CH:38101715027091 YEAR:1983 STC:Hyundai H-1 CH:NLJWWH7JB6Z066963 YEAR:2006 STC:VOLKSWAGEN LT 28 CH:WV2ZZZ28ZMH015144 YEAR:1991 ATTACHED TRAILER ATTACHED</v>
@@ -5214,7 +5214,7 @@
       <c r="K95" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L95">
+      <c r="L95" t="str">
         <v>2005</v>
       </c>
       <c r="M95" t="str">
@@ -5226,8 +5226,8 @@
       <c r="O95">
         <v>2300</v>
       </c>
-      <c r="P95">
-        <v>18.11</v>
+      <c r="P95" t="str">
+        <v>18.110</v>
       </c>
     </row>
     <row r="96">
@@ -5264,7 +5264,7 @@
       <c r="K96" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L96">
+      <c r="L96" t="str">
         <v>2006</v>
       </c>
       <c r="M96" t="str">
@@ -5276,8 +5276,8 @@
       <c r="O96">
         <v>1958</v>
       </c>
-      <c r="P96">
-        <v>17.99</v>
+      <c r="P96" t="str">
+        <v>17.990</v>
       </c>
     </row>
     <row r="97">
@@ -5314,7 +5314,7 @@
       <c r="K97" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L97">
+      <c r="L97" t="str">
         <v>2005</v>
       </c>
       <c r="M97" t="str">
@@ -5326,8 +5326,8 @@
       <c r="O97">
         <v>21360</v>
       </c>
-      <c r="P97">
-        <v>112.62</v>
+      <c r="P97" t="str">
+        <v>112.620</v>
       </c>
       <c r="Q97" t="str">
         <v>STC:DAF 95.360 CH:XLRAS47WS0E377239 YEAR:1992</v>
@@ -5367,7 +5367,7 @@
       <c r="K98" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L98">
+      <c r="L98" t="str">
         <v>1986</v>
       </c>
       <c r="M98" t="str">
@@ -5379,8 +5379,8 @@
       <c r="O98">
         <v>22640</v>
       </c>
-      <c r="P98">
-        <v>100.7</v>
+      <c r="P98" t="str">
+        <v>100.700</v>
       </c>
       <c r="Q98" t="str">
         <v>STC:IVECO MAGIRUS CH:WJME2JSJ00C055095 YEAR:1999</v>
@@ -5420,7 +5420,7 @@
       <c r="K99" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L99">
+      <c r="L99" t="str">
         <v>2007</v>
       </c>
       <c r="M99" t="str">
@@ -5432,8 +5432,8 @@
       <c r="O99">
         <v>2030</v>
       </c>
-      <c r="P99">
-        <v>18.13</v>
+      <c r="P99" t="str">
+        <v>18.130</v>
       </c>
     </row>
     <row r="100">
@@ -5470,7 +5470,7 @@
       <c r="K100" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L100">
+      <c r="L100" t="str">
         <v>2007</v>
       </c>
       <c r="M100" t="str">
@@ -5482,8 +5482,8 @@
       <c r="O100">
         <v>2030</v>
       </c>
-      <c r="P100">
-        <v>18.13</v>
+      <c r="P100" t="str">
+        <v>18.130</v>
       </c>
     </row>
     <row r="101">
@@ -5520,7 +5520,7 @@
       <c r="K101" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L101">
+      <c r="L101" t="str">
         <v>2009</v>
       </c>
       <c r="M101" t="str">
@@ -5532,8 +5532,8 @@
       <c r="O101">
         <v>2030</v>
       </c>
-      <c r="P101">
-        <v>18.13</v>
+      <c r="P101" t="str">
+        <v>18.130</v>
       </c>
     </row>
     <row r="102">
@@ -5570,7 +5570,7 @@
       <c r="K102" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L102">
+      <c r="L102" t="str">
         <v>1998</v>
       </c>
       <c r="M102" t="str">
@@ -5582,8 +5582,8 @@
       <c r="O102">
         <v>1140</v>
       </c>
-      <c r="P102">
-        <v>12.72</v>
+      <c r="P102" t="str">
+        <v>12.720</v>
       </c>
     </row>
     <row r="103">
@@ -5620,7 +5620,7 @@
       <c r="K103" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L103">
+      <c r="L103" t="str">
         <v>1999</v>
       </c>
       <c r="M103" t="str">
@@ -5632,8 +5632,8 @@
       <c r="O103">
         <v>1175</v>
       </c>
-      <c r="P103">
-        <v>10.99</v>
+      <c r="P103" t="str">
+        <v>10.990</v>
       </c>
     </row>
     <row r="104">
@@ -5670,7 +5670,7 @@
       <c r="K104" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L104">
+      <c r="L104" t="str">
         <v>2010</v>
       </c>
       <c r="M104" t="str">
@@ -5682,8 +5682,8 @@
       <c r="O104">
         <v>33640</v>
       </c>
-      <c r="P104">
-        <v>145.95</v>
+      <c r="P104" t="str">
+        <v>145.950</v>
       </c>
       <c r="Q104" t="str">
         <v>STC:VOLVO FL6 CH:YB1E6A114KB444573 YEAR:1989 STC:VOLVO FL6 CH:YB1E6A2A1GB400407 YEAR:1986 STC:VOLVO FL6 CH:YV2E4C318XB229031 YEAR:1999 STC:IVECO EUROCARGO CH:ZCFA1LG0002107218 YEAR:1994</v>
@@ -5723,7 +5723,7 @@
       <c r="K105" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L105">
+      <c r="L105" t="str">
         <v>2003</v>
       </c>
       <c r="M105" t="str">
@@ -5735,8 +5735,8 @@
       <c r="O105">
         <v>11140</v>
       </c>
-      <c r="P105">
-        <v>81.94</v>
+      <c r="P105" t="str">
+        <v>81.940</v>
       </c>
       <c r="Q105" t="str">
         <v>STC:PEUGEOT BOXER CH:VF3290J5200403664 YEAR:2003</v>
@@ -5776,7 +5776,7 @@
       <c r="K106" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L106">
+      <c r="L106" t="str">
         <v>1992</v>
       </c>
       <c r="M106" t="str">
@@ -5788,8 +5788,8 @@
       <c r="O106">
         <v>13660</v>
       </c>
-      <c r="P106">
-        <v>113.1</v>
+      <c r="P106" t="str">
+        <v>113.100</v>
       </c>
       <c r="Q106" t="str">
         <v>STC:PEUGEOT J5 CH:VF329085200012353 YEAR:1990 STC:MERCEDES-BENZ 1114 CH:WDB67501215553988 YEAR:1992</v>
@@ -5829,7 +5829,7 @@
       <c r="K107" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L107">
+      <c r="L107" t="str">
         <v>1984</v>
       </c>
       <c r="M107" t="str">
@@ -5841,8 +5841,8 @@
       <c r="O107">
         <v>17600</v>
       </c>
-      <c r="P107">
-        <v>86.85</v>
+      <c r="P107" t="str">
+        <v>86.850</v>
       </c>
       <c r="Q107" t="str">
         <v>STC:Lexus RX 300 CH:JTJHF31U202001477 YEAR:2005</v>
@@ -5882,7 +5882,7 @@
       <c r="K108" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L108">
+      <c r="L108" t="str">
         <v>1995</v>
       </c>
       <c r="M108" t="str">
@@ -5894,8 +5894,8 @@
       <c r="O108">
         <v>10800</v>
       </c>
-      <c r="P108">
-        <v>67.52</v>
+      <c r="P108" t="str">
+        <v>67.520</v>
       </c>
       <c r="Q108" t="str">
         <v>STC:CITROEN C25 CH:VF7290K52UD436678 YEAR:1993 STC:UNIC TRUCK CH:ZCFA6580002000869 YEAR:1991</v>
@@ -5935,7 +5935,7 @@
       <c r="K109" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L109">
+      <c r="L109" t="str">
         <v>1998</v>
       </c>
       <c r="M109" t="str">
@@ -5947,8 +5947,8 @@
       <c r="O109">
         <v>1763</v>
       </c>
-      <c r="P109">
-        <v>15.31</v>
+      <c r="P109" t="str">
+        <v>15.310</v>
       </c>
     </row>
     <row r="110">
@@ -5985,7 +5985,7 @@
       <c r="K110" t="str">
         <v>Sarne As Consignee</v>
       </c>
-      <c r="L110">
+      <c r="L110" t="str">
         <v>2008</v>
       </c>
       <c r="M110" t="str">
@@ -5997,8 +5997,8 @@
       <c r="O110">
         <v>1135</v>
       </c>
-      <c r="P110">
-        <v>9.05</v>
+      <c r="P110" t="str">
+        <v>9.050</v>
       </c>
     </row>
     <row r="111">
@@ -6035,7 +6035,7 @@
       <c r="K111" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L111">
+      <c r="L111" t="str">
         <v>1992</v>
       </c>
       <c r="M111" t="str">
@@ -6047,8 +6047,8 @@
       <c r="O111">
         <v>6875</v>
       </c>
-      <c r="P111">
-        <v>57</v>
+      <c r="P111" t="str">
+        <v>57.000</v>
       </c>
     </row>
     <row r="112">
@@ -6085,7 +6085,7 @@
       <c r="K112" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L112">
+      <c r="L112" t="str">
         <v>2005</v>
       </c>
       <c r="M112" t="str">
@@ -6097,8 +6097,8 @@
       <c r="O112">
         <v>12070</v>
       </c>
-      <c r="P112">
-        <v>99.75</v>
+      <c r="P112" t="str">
+        <v>99.750</v>
       </c>
     </row>
     <row r="113">
@@ -6135,7 +6135,7 @@
       <c r="K113" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L113">
+      <c r="L113" t="str">
         <v>2003</v>
       </c>
       <c r="M113" t="str">
@@ -6147,8 +6147,8 @@
       <c r="O113">
         <v>17140</v>
       </c>
-      <c r="P113">
-        <v>76.92</v>
+      <c r="P113" t="str">
+        <v>76.920</v>
       </c>
       <c r="Q113" t="str">
         <v>STC:AGRICULTURE TRACTOR CH:849926 YEAR:1976</v>
@@ -6188,7 +6188,7 @@
       <c r="K114" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L114">
+      <c r="L114" t="str">
         <v>1980</v>
       </c>
       <c r="M114" t="str">
@@ -6200,8 +6200,8 @@
       <c r="O114">
         <v>4500</v>
       </c>
-      <c r="P114">
-        <v>20.25</v>
+      <c r="P114" t="str">
+        <v>20.250</v>
       </c>
     </row>
     <row r="115">
@@ -6238,7 +6238,7 @@
       <c r="K115" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L115">
+      <c r="L115" t="str">
         <v>1990</v>
       </c>
       <c r="M115" t="str">
@@ -6250,8 +6250,8 @@
       <c r="O115">
         <v>4500</v>
       </c>
-      <c r="P115">
-        <v>18.83</v>
+      <c r="P115" t="str">
+        <v>18.830</v>
       </c>
     </row>
     <row r="116">
@@ -6288,7 +6288,7 @@
       <c r="K116" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L116">
+      <c r="L116" t="str">
         <v>2000</v>
       </c>
       <c r="M116" t="str">
@@ -6300,8 +6300,8 @@
       <c r="O116">
         <v>9380</v>
       </c>
-      <c r="P116">
-        <v>100</v>
+      <c r="P116" t="str">
+        <v>100.000</v>
       </c>
       <c r="Q116" t="str">
         <v>STC:Toyota Dyna CH:JT1P0LH8009109949 YEAR:1991 STC:DAF 75 CH:XLRAE75PC0E536171 YEAR:2001</v>
@@ -6341,7 +6341,7 @@
       <c r="K117" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L117">
+      <c r="L117" t="str">
         <v>1993</v>
       </c>
       <c r="M117" t="str">
@@ -6353,8 +6353,8 @@
       <c r="O117">
         <v>19120</v>
       </c>
-      <c r="P117">
-        <v>75.49</v>
+      <c r="P117" t="str">
+        <v>75.490</v>
       </c>
     </row>
     <row r="118">
@@ -6391,7 +6391,7 @@
       <c r="K118" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L118">
+      <c r="L118" t="str">
         <v>1993</v>
       </c>
       <c r="M118" t="str">
@@ -6403,8 +6403,8 @@
       <c r="O118">
         <v>11180</v>
       </c>
-      <c r="P118">
-        <v>56.34</v>
+      <c r="P118" t="str">
+        <v>56.340</v>
       </c>
       <c r="Q118" t="str">
         <v>STC:PERSONAL GOODS</v>
@@ -6444,7 +6444,7 @@
       <c r="K119" t="str">
         <v>SAME AS CONSIGNEE</v>
       </c>
-      <c r="L119">
+      <c r="L119" t="str">
         <v>2025</v>
       </c>
       <c r="M119" t="str">
@@ -6456,8 +6456,8 @@
       <c r="O119">
         <v>10300</v>
       </c>
-      <c r="P119">
-        <v>44.58</v>
+      <c r="P119" t="str">
+        <v>44.580</v>
       </c>
       <c r="Q119" t="str">
         <v>STC:1 CRATE MAINTENANCE KIT CH:3321940CRATE WE:41 KG YEAR:2025</v>
@@ -6497,7 +6497,7 @@
       <c r="K120" t="str">
         <v>SAME AS CONSIGNEE</v>
       </c>
-      <c r="L120">
+      <c r="L120" t="str">
         <v>2025</v>
       </c>
       <c r="M120" t="str">
@@ -6509,8 +6509,8 @@
       <c r="O120">
         <v>10300</v>
       </c>
-      <c r="P120">
-        <v>44.58</v>
+      <c r="P120" t="str">
+        <v>44.580</v>
       </c>
       <c r="Q120" t="str">
         <v>STC:1 CRATE MAINTENANCE KIT CH:3321941CRATE WE:41 KG YEAR:2025 FORM M BA057 2025 3018778/ MF20250130820</v>
@@ -6550,7 +6550,7 @@
       <c r="K121" t="str">
         <v>Sarne As Consignee</v>
       </c>
-      <c r="L121">
+      <c r="L121" t="str">
         <v>1993</v>
       </c>
       <c r="M121" t="str">
@@ -6562,8 +6562,8 @@
       <c r="O121">
         <v>15250</v>
       </c>
-      <c r="P121">
-        <v>91.68</v>
+      <c r="P121" t="str">
+        <v>91.680</v>
       </c>
       <c r="Q121" t="str">
         <v>STC:MERCEDES-BENZ 1413 CH:WDB34000210621326</v>
@@ -6603,7 +6603,7 @@
       <c r="K122" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L122">
+      <c r="L122" t="str">
         <v>2017</v>
       </c>
       <c r="M122" t="str">
@@ -6615,8 +6615,8 @@
       <c r="O122">
         <v>1426</v>
       </c>
-      <c r="P122">
-        <v>13.4</v>
+      <c r="P122" t="str">
+        <v>13.400</v>
       </c>
     </row>
     <row r="123">
@@ -6653,7 +6653,7 @@
       <c r="K123" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L123">
+      <c r="L123" t="str">
         <v>1979</v>
       </c>
       <c r="M123" t="str">
@@ -6665,8 +6665,8 @@
       <c r="O123">
         <v>9740</v>
       </c>
-      <c r="P123">
-        <v>47.44</v>
+      <c r="P123" t="str">
+        <v>47.440</v>
       </c>
       <c r="Q123" t="str">
         <v>STC:Toyota Avensis CH:SB1EJ56L00E021388</v>
@@ -6706,7 +6706,7 @@
       <c r="K124" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L124">
+      <c r="L124" t="str">
         <v>2006</v>
       </c>
       <c r="M124" t="str">
@@ -6718,8 +6718,8 @@
       <c r="O124">
         <v>1500</v>
       </c>
-      <c r="P124">
-        <v>12.56</v>
+      <c r="P124" t="str">
+        <v>12.560</v>
       </c>
     </row>
     <row r="125">
@@ -6756,7 +6756,7 @@
       <c r="K125" t="str">
         <v>SAME AS CONSIGNEE</v>
       </c>
-      <c r="L125">
+      <c r="L125" t="str">
         <v>2007</v>
       </c>
       <c r="M125" t="str">
@@ -6768,8 +6768,8 @@
       <c r="O125">
         <v>7980</v>
       </c>
-      <c r="P125">
-        <v>51.15</v>
+      <c r="P125" t="str">
+        <v>51.150</v>
       </c>
       <c r="Q125" t="str">
         <v>STC:Suzuki Alto CH:MA3FFB21S00217948</v>
@@ -6809,7 +6809,7 @@
       <c r="K126" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L126">
+      <c r="L126" t="str">
         <v>2003</v>
       </c>
       <c r="M126" t="str">
@@ -6821,8 +6821,8 @@
       <c r="O126">
         <v>2350</v>
       </c>
-      <c r="P126">
-        <v>28.14</v>
+      <c r="P126" t="str">
+        <v>28.140</v>
       </c>
     </row>
     <row r="127">
@@ -6859,7 +6859,7 @@
       <c r="K127" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L127">
+      <c r="L127" t="str">
         <v>2006</v>
       </c>
       <c r="M127" t="str">
@@ -6871,8 +6871,8 @@
       <c r="O127">
         <v>2200</v>
       </c>
-      <c r="P127">
-        <v>26.57</v>
+      <c r="P127" t="str">
+        <v>26.570</v>
       </c>
     </row>
     <row r="128">
@@ -6909,7 +6909,7 @@
       <c r="K128" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L128">
+      <c r="L128" t="str">
         <v>2003</v>
       </c>
       <c r="M128" t="str">
@@ -6921,8 +6921,8 @@
       <c r="O128">
         <v>3500</v>
       </c>
-      <c r="P128">
-        <v>27.63</v>
+      <c r="P128" t="str">
+        <v>27.630</v>
       </c>
     </row>
     <row r="129">
@@ -6959,7 +6959,7 @@
       <c r="K129" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L129">
+      <c r="L129" t="str">
         <v>1999</v>
       </c>
       <c r="M129" t="str">
@@ -6971,8 +6971,8 @@
       <c r="O129">
         <v>2200</v>
       </c>
-      <c r="P129">
-        <v>26.04</v>
+      <c r="P129" t="str">
+        <v>26.040</v>
       </c>
     </row>
     <row r="130">
@@ -7009,7 +7009,7 @@
       <c r="K130" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L130">
+      <c r="L130" t="str">
         <v>2002</v>
       </c>
       <c r="M130" t="str">
@@ -7021,8 +7021,8 @@
       <c r="O130">
         <v>2300</v>
       </c>
-      <c r="P130">
-        <v>26.4</v>
+      <c r="P130" t="str">
+        <v>26.400</v>
       </c>
     </row>
     <row r="131">
@@ -7059,7 +7059,7 @@
       <c r="K131" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L131">
+      <c r="L131" t="str">
         <v>1985</v>
       </c>
       <c r="M131" t="str">
@@ -7071,8 +7071,8 @@
       <c r="O131">
         <v>27680</v>
       </c>
-      <c r="P131">
-        <v>82.36</v>
+      <c r="P131" t="str">
+        <v>82.360</v>
       </c>
     </row>
     <row r="132">
@@ -7109,7 +7109,7 @@
       <c r="K132" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L132">
+      <c r="L132" t="str">
         <v>2003</v>
       </c>
       <c r="M132" t="str">
@@ -7121,8 +7121,8 @@
       <c r="O132">
         <v>20820</v>
       </c>
-      <c r="P132">
-        <v>114.92</v>
+      <c r="P132" t="str">
+        <v>114.920</v>
       </c>
       <c r="Q132" t="str">
         <v>STC:Mercedes Truck CH:WDB9505041K490518 YEAR:2001</v>
@@ -7162,7 +7162,7 @@
       <c r="K133" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L133">
+      <c r="L133" t="str">
         <v>2005</v>
       </c>
       <c r="M133" t="str">
@@ -7174,8 +7174,8 @@
       <c r="O133">
         <v>2300</v>
       </c>
-      <c r="P133">
-        <v>28.34</v>
+      <c r="P133" t="str">
+        <v>28.340</v>
       </c>
     </row>
     <row r="134">
@@ -7212,7 +7212,7 @@
       <c r="K134" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L134">
+      <c r="L134" t="str">
         <v>2006</v>
       </c>
       <c r="M134" t="str">
@@ -7224,8 +7224,8 @@
       <c r="O134">
         <v>2350</v>
       </c>
-      <c r="P134">
-        <v>27.08</v>
+      <c r="P134" t="str">
+        <v>27.080</v>
       </c>
     </row>
     <row r="135">
@@ -7262,7 +7262,7 @@
       <c r="K135" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L135">
+      <c r="L135" t="str">
         <v>1996</v>
       </c>
       <c r="M135" t="str">
@@ -7274,8 +7274,8 @@
       <c r="O135">
         <v>16500</v>
       </c>
-      <c r="P135">
-        <v>84.38</v>
+      <c r="P135" t="str">
+        <v>84.380</v>
       </c>
       <c r="Q135" t="str">
         <v>STC:MAN TRUCK CH:WMA5093230M021566 YEAR:1984</v>
@@ -7315,7 +7315,7 @@
       <c r="K136" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L136">
+      <c r="L136" t="str">
         <v>1985</v>
       </c>
       <c r="M136" t="str">
@@ -7327,8 +7327,8 @@
       <c r="O136">
         <v>22760</v>
       </c>
-      <c r="P136">
-        <v>93.6</v>
+      <c r="P136" t="str">
+        <v>93.600</v>
       </c>
       <c r="Q136" t="str">
         <v>STC:SCANIA TRUCK R112 CH:RA4X2A01057999 YEAR:1982 STC:Volkswagen Golf CH:ZZZ1HZTW456530 YEAR:1996 STC:VOLVO FL6 CH:E6A8AOLB452998</v>
@@ -7368,7 +7368,7 @@
       <c r="K137" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L137">
+      <c r="L137" t="str">
         <v>1999</v>
       </c>
       <c r="M137" t="str">
@@ -7380,8 +7380,8 @@
       <c r="O137">
         <v>2175</v>
       </c>
-      <c r="P137">
-        <v>15.54</v>
+      <c r="P137" t="str">
+        <v>15.540</v>
       </c>
     </row>
     <row r="138">
@@ -7418,7 +7418,7 @@
       <c r="K138" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L138">
+      <c r="L138" t="str">
         <v>1998</v>
       </c>
       <c r="M138" t="str">
@@ -7430,8 +7430,8 @@
       <c r="O138">
         <v>1570</v>
       </c>
-      <c r="P138">
-        <v>19.9</v>
+      <c r="P138" t="str">
+        <v>19.900</v>
       </c>
     </row>
     <row r="139">
@@ -7468,7 +7468,7 @@
       <c r="K139" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L139">
+      <c r="L139" t="str">
         <v>1999</v>
       </c>
       <c r="M139" t="str">
@@ -7480,8 +7480,8 @@
       <c r="O139">
         <v>2000</v>
       </c>
-      <c r="P139">
-        <v>21.18</v>
+      <c r="P139" t="str">
+        <v>21.180</v>
       </c>
     </row>
     <row r="140">
@@ -7518,7 +7518,7 @@
       <c r="K140" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L140">
+      <c r="L140" t="str">
         <v>1981</v>
       </c>
       <c r="M140" t="str">
@@ -7530,8 +7530,8 @@
       <c r="O140">
         <v>15220</v>
       </c>
-      <c r="P140">
-        <v>87.19</v>
+      <c r="P140" t="str">
+        <v>87.190</v>
       </c>
     </row>
     <row r="141">
@@ -7568,7 +7568,7 @@
       <c r="K141" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L141">
+      <c r="L141" t="str">
         <v>2005</v>
       </c>
       <c r="M141" t="str">
@@ -7580,8 +7580,8 @@
       <c r="O141">
         <v>1500</v>
       </c>
-      <c r="P141">
-        <v>12.56</v>
+      <c r="P141" t="str">
+        <v>12.560</v>
       </c>
     </row>
     <row r="142">
@@ -7618,7 +7618,7 @@
       <c r="K142" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L142">
+      <c r="L142" t="str">
         <v>2005</v>
       </c>
       <c r="M142" t="str">
@@ -7630,8 +7630,8 @@
       <c r="O142">
         <v>1235</v>
       </c>
-      <c r="P142">
-        <v>12.16</v>
+      <c r="P142" t="str">
+        <v>12.160</v>
       </c>
     </row>
     <row r="143">
@@ -7668,7 +7668,7 @@
       <c r="K143" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L143">
+      <c r="L143" t="str">
         <v>2000</v>
       </c>
       <c r="M143" t="str">
@@ -7680,8 +7680,8 @@
       <c r="O143">
         <v>11900</v>
       </c>
-      <c r="P143">
-        <v>84.44</v>
+      <c r="P143" t="str">
+        <v>84.440</v>
       </c>
       <c r="Q143" t="str">
         <v>STC:MERCEDES-BENZ 809 CH:WDB67301018494986 YEAR:2000 STC:Toyota Yaris CH:VNKKL98350A313016 YEAR:2008</v>
@@ -7721,7 +7721,7 @@
       <c r="K144" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L144">
+      <c r="L144" t="str">
         <v>2000</v>
       </c>
       <c r="M144" t="str">
@@ -7733,8 +7733,8 @@
       <c r="O144">
         <v>9720</v>
       </c>
-      <c r="P144">
-        <v>82.35</v>
+      <c r="P144" t="str">
+        <v>82.350</v>
       </c>
       <c r="Q144" t="str">
         <v>STC:Suzuki Wagon R CH:TSMMMA33500282290 YEAR:2000 STC:CITROEN JUMPER CH:VF7ZCPMNC17410592 YEAR:2000</v>
@@ -7774,7 +7774,7 @@
       <c r="K145" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L145">
+      <c r="L145" t="str">
         <v>1990</v>
       </c>
       <c r="M145" t="str">
@@ -7786,8 +7786,8 @@
       <c r="O145">
         <v>23320</v>
       </c>
-      <c r="P145">
-        <v>106</v>
+      <c r="P145" t="str">
+        <v>106.000</v>
       </c>
       <c r="Q145" t="str">
         <v>STC:IVECO TRUCK CH:ZCFE2JPH104125003 YEAR:2000</v>
@@ -7827,7 +7827,7 @@
       <c r="K146" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L146">
+      <c r="L146" t="str">
         <v>2013</v>
       </c>
       <c r="M146" t="str">
@@ -7839,8 +7839,8 @@
       <c r="O146">
         <v>12620</v>
       </c>
-      <c r="P146">
-        <v>65.45</v>
+      <c r="P146" t="str">
+        <v>65.450</v>
       </c>
     </row>
     <row r="147">
@@ -7877,7 +7877,7 @@
       <c r="K147" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L147">
+      <c r="L147" t="str">
         <v>2000</v>
       </c>
       <c r="M147" t="str">
@@ -7889,8 +7889,8 @@
       <c r="O147">
         <v>19500</v>
       </c>
-      <c r="P147">
-        <v>79.03</v>
+      <c r="P147" t="str">
+        <v>79.030</v>
       </c>
     </row>
     <row r="148">
@@ -7927,7 +7927,7 @@
       <c r="K148" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L148">
+      <c r="L148" t="str">
         <v>2004</v>
       </c>
       <c r="M148" t="str">
@@ -7939,8 +7939,8 @@
       <c r="O148">
         <v>9300</v>
       </c>
-      <c r="P148">
-        <v>68.66</v>
+      <c r="P148" t="str">
+        <v>68.660</v>
       </c>
       <c r="Q148" t="str">
         <v>STC:Mercedes A180 CH:WDB1680331J281340 YEAR:2000</v>
@@ -7980,7 +7980,7 @@
       <c r="K149" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L149">
+      <c r="L149" t="str">
         <v>2000</v>
       </c>
       <c r="M149" t="str">
@@ -7992,8 +7992,8 @@
       <c r="O149">
         <v>11400</v>
       </c>
-      <c r="P149">
-        <v>66.56</v>
+      <c r="P149" t="str">
+        <v>66.560</v>
       </c>
     </row>
     <row r="150">
@@ -8030,7 +8030,7 @@
       <c r="K150" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L150">
+      <c r="L150" t="str">
         <v>2000</v>
       </c>
       <c r="M150" t="str">
@@ -8042,8 +8042,8 @@
       <c r="O150">
         <v>8520</v>
       </c>
-      <c r="P150">
-        <v>75.22</v>
+      <c r="P150" t="str">
+        <v>75.220</v>
       </c>
       <c r="Q150" t="str">
         <v>STC:Nissan Micra CH:S1NEAAK11U4233918 YEAR:2002 STC:MERCEDES-BENZ 711D CH:WDB6693031P199662 YEAR:2000</v>
@@ -8083,7 +8083,7 @@
       <c r="K151" t="str">
         <v>Sarne As Consignee</v>
       </c>
-      <c r="L151">
+      <c r="L151" t="str">
         <v>2003</v>
       </c>
       <c r="M151" t="str">
@@ -8095,8 +8095,8 @@
       <c r="O151">
         <v>17800</v>
       </c>
-      <c r="P151">
-        <v>121.55</v>
+      <c r="P151" t="str">
+        <v>121.550</v>
       </c>
       <c r="Q151" t="str">
         <v>STC:RENAULT MASTER CH:VF1FDCUL528377723 YEAR:2003 STC:DAF TRUCK CH:XLRAE55GF0L357448 YEAR:2000</v>
@@ -8136,7 +8136,7 @@
       <c r="K152" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L152">
+      <c r="L152" t="str">
         <v>2000</v>
       </c>
       <c r="M152" t="str">
@@ -8148,8 +8148,8 @@
       <c r="O152">
         <v>8280</v>
       </c>
-      <c r="P152">
-        <v>60.22</v>
+      <c r="P152" t="str">
+        <v>60.220</v>
       </c>
       <c r="Q152" t="str">
         <v>STC:Kia Picanto CH:KNEBA24336T252032 YEAR:2003 STC:PEUGEOT BOXER CH:VF323314215705191</v>
@@ -8189,7 +8189,7 @@
       <c r="K153" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L153">
+      <c r="L153" t="str">
         <v>2001</v>
       </c>
       <c r="M153" t="str">
@@ -8201,8 +8201,8 @@
       <c r="O153">
         <v>22320</v>
       </c>
-      <c r="P153">
-        <v>128.56</v>
+      <c r="P153" t="str">
+        <v>128.560</v>
       </c>
       <c r="Q153" t="str">
         <v>STC:Peugeot 307 CH:VF33CNFUB82283117 YEAR:2001 ATTACHED:TRAILER ATTACHED CH:VFNS332ENK1L02609 YEAR:1989 STC:TRAILER LOOSE</v>
@@ -8242,7 +8242,7 @@
       <c r="K154" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L154">
+      <c r="L154" t="str">
         <v>1994</v>
       </c>
       <c r="M154" t="str">
@@ -8254,8 +8254,8 @@
       <c r="O154">
         <v>22760</v>
       </c>
-      <c r="P154">
-        <v>119.9</v>
+      <c r="P154" t="str">
+        <v>119.900</v>
       </c>
       <c r="Q154" t="str">
         <v>STC: MERCEDES-BENZ 609 CH:WDB6693021P005629 YEAR:1992 STC:MAN TRUCK CH:WMAF098730M168552 YEAR:1994</v>
@@ -8295,7 +8295,7 @@
       <c r="K155" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L155">
+      <c r="L155" t="str">
         <v>1996</v>
       </c>
       <c r="M155" t="str">
@@ -8307,8 +8307,8 @@
       <c r="O155">
         <v>15240</v>
       </c>
-      <c r="P155">
-        <v>88.15</v>
+      <c r="P155" t="str">
+        <v>88.150</v>
       </c>
       <c r="Q155" t="str">
         <v>STC: Mercedes Truck CH:WDB6760071K175765 YEAR:1996 STC:Toyota Corolla CH:SB1KZ28E30E021782 YEAR:2002</v>
@@ -8348,7 +8348,7 @@
       <c r="K156" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L156">
+      <c r="L156" t="str">
         <v>1990</v>
       </c>
       <c r="M156" t="str">
@@ -8360,8 +8360,8 @@
       <c r="O156">
         <v>5040</v>
       </c>
-      <c r="P156">
-        <v>56.71</v>
+      <c r="P156" t="str">
+        <v>56.710</v>
       </c>
     </row>
     <row r="157">
@@ -8398,7 +8398,7 @@
       <c r="K157" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L157">
+      <c r="L157" t="str">
         <v>2006</v>
       </c>
       <c r="M157" t="str">
@@ -8410,8 +8410,8 @@
       <c r="O157">
         <v>10200</v>
       </c>
-      <c r="P157">
-        <v>78.41</v>
+      <c r="P157" t="str">
+        <v>78.410</v>
       </c>
       <c r="Q157" t="str">
         <v>STC:Renault Trafic CH:VF1TBXG0513069869 YEAR:1995 STC:Opel Agila CH:W0L0HAF685G106736 YEAR:2005</v>
@@ -8451,7 +8451,7 @@
       <c r="K158" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L158">
+      <c r="L158" t="str">
         <v>1981</v>
       </c>
       <c r="M158" t="str">
@@ -8463,8 +8463,8 @@
       <c r="O158">
         <v>19720</v>
       </c>
-      <c r="P158">
-        <v>99.22</v>
+      <c r="P158" t="str">
+        <v>99.220</v>
       </c>
       <c r="Q158" t="str">
         <v>STC:DAF TRUCK CH:168897 YEAR:1978 STC:VOLVO TRUCK CH:YV2E4C6A3XB213234 YEAR:1998</v>
@@ -8504,7 +8504,7 @@
       <c r="K159" t="str">
         <v>Sarne As Consignee</v>
       </c>
-      <c r="L159">
+      <c r="L159" t="str">
         <v>1996</v>
       </c>
       <c r="M159" t="str">
@@ -8516,8 +8516,8 @@
       <c r="O159">
         <v>11600</v>
       </c>
-      <c r="P159">
-        <v>78.5</v>
+      <c r="P159" t="str">
+        <v>78.500</v>
       </c>
       <c r="Q159" t="str">
         <v>STC:MAN TRUCK CH:WMA4981033M046440 YEAR:1986</v>
@@ -8557,7 +8557,7 @@
       <c r="K160" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L160">
+      <c r="L160" t="str">
         <v>1998</v>
       </c>
       <c r="M160" t="str">
@@ -8569,8 +8569,8 @@
       <c r="O160">
         <v>17160</v>
       </c>
-      <c r="P160">
-        <v>107</v>
+      <c r="P160" t="str">
+        <v>107.000</v>
       </c>
       <c r="Q160" t="str">
         <v>STC:Mercedes-Benz Sprinter CH:WDF9066351A980077 YEAR:2008</v>
@@ -8610,7 +8610,7 @@
       <c r="K161" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L161">
+      <c r="L161" t="str">
         <v>2002</v>
       </c>
       <c r="M161" t="str">
@@ -8622,8 +8622,8 @@
       <c r="O161">
         <v>16960</v>
       </c>
-      <c r="P161">
-        <v>117.7</v>
+      <c r="P161" t="str">
+        <v>117.700</v>
       </c>
       <c r="Q161" t="str">
         <v>STC: MERCEDES-BENZ 814 CH:WDB67401415258717 YEAR:1986</v>
@@ -8663,7 +8663,7 @@
       <c r="K162" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L162">
+      <c r="L162" t="str">
         <v>1980</v>
       </c>
       <c r="M162" t="str">
@@ -8675,8 +8675,8 @@
       <c r="O162">
         <v>6100</v>
       </c>
-      <c r="P162">
-        <v>62.42</v>
+      <c r="P162" t="str">
+        <v>62.420</v>
       </c>
     </row>
     <row r="163">
@@ -8713,7 +8713,7 @@
       <c r="K163" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L163">
+      <c r="L163" t="str">
         <v>2003</v>
       </c>
       <c r="M163" t="str">
@@ -8725,8 +8725,8 @@
       <c r="O163">
         <v>10320</v>
       </c>
-      <c r="P163">
-        <v>57.6</v>
+      <c r="P163" t="str">
+        <v>57.600</v>
       </c>
     </row>
     <row r="164">
@@ -8763,7 +8763,7 @@
       <c r="K164" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L164">
+      <c r="L164" t="str">
         <v>1994</v>
       </c>
       <c r="M164" t="str">
@@ -8775,8 +8775,8 @@
       <c r="O164">
         <v>7700</v>
       </c>
-      <c r="P164">
-        <v>48.3</v>
+      <c r="P164" t="str">
+        <v>48.300</v>
       </c>
     </row>
     <row r="165">
@@ -8813,7 +8813,7 @@
       <c r="K165" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L165">
+      <c r="L165" t="str">
         <v>2007</v>
       </c>
       <c r="M165" t="str">
@@ -8825,8 +8825,8 @@
       <c r="O165">
         <v>35880</v>
       </c>
-      <c r="P165">
-        <v>181.5</v>
+      <c r="P165" t="str">
+        <v>181.500</v>
       </c>
       <c r="Q165" t="str">
         <v>STC:TRACTOR GENERAL JOHN DEERE CH:00000000000052463 YEAR:2000 ATTACHED:TRAILER GENERAL CH:WK0S0002400137636 YEAR:2000 STC:DAF 85 CH:XLRA585XC0E593649 YEAR:2000 STC:DAF XF TRUCK CH:XLRTE47MS0E814449 YEAR:2000</v>
@@ -8866,7 +8866,7 @@
       <c r="K166" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L166">
+      <c r="L166" t="str">
         <v>2000</v>
       </c>
       <c r="M166" t="str">
@@ -8878,8 +8878,8 @@
       <c r="O166">
         <v>52100</v>
       </c>
-      <c r="P166">
-        <v>137.94</v>
+      <c r="P166" t="str">
+        <v>137.940</v>
       </c>
     </row>
     <row r="167">
@@ -8916,7 +8916,7 @@
       <c r="K167" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L167">
+      <c r="L167" t="str">
         <v>1999</v>
       </c>
       <c r="M167" t="str">
@@ -8928,8 +8928,8 @@
       <c r="O167">
         <v>16000</v>
       </c>
-      <c r="P167">
-        <v>114.49</v>
+      <c r="P167" t="str">
+        <v>114.490</v>
       </c>
       <c r="Q167" t="str">
         <v>STC:MAN TRUCK CH:WMAM330572Y044940 YEAR:1999</v>
@@ -8969,7 +8969,7 @@
       <c r="K168" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L168">
+      <c r="L168" t="str">
         <v>1991</v>
       </c>
       <c r="M168" t="str">
@@ -8981,8 +8981,8 @@
       <c r="O168">
         <v>27500</v>
       </c>
-      <c r="P168">
-        <v>47.99</v>
+      <c r="P168" t="str">
+        <v>47.990</v>
       </c>
       <c r="Q168" t="str">
         <v>SHIPPED ALONG WITH 5 LOOSE PIECES - BEAM-BEAM-BLADE-FOOT PIECE - FOOT PIECE</v>
@@ -9022,7 +9022,7 @@
       <c r="K169" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L169">
+      <c r="L169" t="str">
         <v>2002</v>
       </c>
       <c r="M169" t="str">
@@ -9034,8 +9034,8 @@
       <c r="O169">
         <v>1317</v>
       </c>
-      <c r="P169">
-        <v>11.34</v>
+      <c r="P169" t="str">
+        <v>11.340</v>
       </c>
     </row>
     <row r="170">
@@ -9072,7 +9072,7 @@
       <c r="K170" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L170">
+      <c r="L170" t="str">
         <v>2000</v>
       </c>
       <c r="M170" t="str">
@@ -9084,8 +9084,8 @@
       <c r="O170">
         <v>1568</v>
       </c>
-      <c r="P170">
-        <v>11.74</v>
+      <c r="P170" t="str">
+        <v>11.740</v>
       </c>
     </row>
     <row r="171">
@@ -9122,7 +9122,7 @@
       <c r="K171" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L171">
+      <c r="L171" t="str">
         <v>2003</v>
       </c>
       <c r="M171" t="str">
@@ -9134,8 +9134,8 @@
       <c r="O171">
         <v>1465</v>
       </c>
-      <c r="P171">
-        <v>11.29</v>
+      <c r="P171" t="str">
+        <v>11.290</v>
       </c>
     </row>
     <row r="172">
@@ -9172,7 +9172,7 @@
       <c r="K172" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L172">
+      <c r="L172" t="str">
         <v>2004</v>
       </c>
       <c r="M172" t="str">
@@ -9184,8 +9184,8 @@
       <c r="O172">
         <v>2100</v>
       </c>
-      <c r="P172">
-        <v>18.99</v>
+      <c r="P172" t="str">
+        <v>18.990</v>
       </c>
     </row>
     <row r="173">
@@ -9222,7 +9222,7 @@
       <c r="K173" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L173">
+      <c r="L173" t="str">
         <v>2006</v>
       </c>
       <c r="M173" t="str">
@@ -9234,8 +9234,8 @@
       <c r="O173">
         <v>1755</v>
       </c>
-      <c r="P173">
-        <v>18.43</v>
+      <c r="P173" t="str">
+        <v>18.430</v>
       </c>
     </row>
     <row r="174">
@@ -9272,7 +9272,7 @@
       <c r="K174" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L174">
+      <c r="L174" t="str">
         <v>2011</v>
       </c>
       <c r="M174" t="str">
@@ -9284,8 +9284,8 @@
       <c r="O174">
         <v>1755</v>
       </c>
-      <c r="P174">
-        <v>17.19</v>
+      <c r="P174" t="str">
+        <v>17.190</v>
       </c>
     </row>
     <row r="175">
@@ -9322,7 +9322,7 @@
       <c r="K175" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L175">
+      <c r="L175" t="str">
         <v>2006</v>
       </c>
       <c r="M175" t="str">
@@ -9334,8 +9334,8 @@
       <c r="O175">
         <v>1170</v>
       </c>
-      <c r="P175">
-        <v>10.73</v>
+      <c r="P175" t="str">
+        <v>10.730</v>
       </c>
     </row>
     <row r="176">
@@ -9372,7 +9372,7 @@
       <c r="K176" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L176">
+      <c r="L176" t="str">
         <v>2008</v>
       </c>
       <c r="M176" t="str">
@@ -9384,8 +9384,8 @@
       <c r="O176">
         <v>1402</v>
       </c>
-      <c r="P176">
-        <v>13.54</v>
+      <c r="P176" t="str">
+        <v>13.540</v>
       </c>
     </row>
     <row r="177">
@@ -9422,7 +9422,7 @@
       <c r="K177" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L177">
+      <c r="L177" t="str">
         <v>2008</v>
       </c>
       <c r="M177" t="str">
@@ -9434,8 +9434,8 @@
       <c r="O177">
         <v>1078</v>
       </c>
-      <c r="P177">
-        <v>10.98</v>
+      <c r="P177" t="str">
+        <v>10.980</v>
       </c>
     </row>
     <row r="178">
@@ -9472,7 +9472,7 @@
       <c r="K178" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L178">
+      <c r="L178" t="str">
         <v>2001</v>
       </c>
       <c r="M178" t="str">
@@ -9484,8 +9484,8 @@
       <c r="O178">
         <v>1763</v>
       </c>
-      <c r="P178">
-        <v>15.31</v>
+      <c r="P178" t="str">
+        <v>15.310</v>
       </c>
     </row>
     <row r="179">
@@ -9522,7 +9522,7 @@
       <c r="K179" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L179">
+      <c r="L179" t="str">
         <v>2001</v>
       </c>
       <c r="M179" t="str">
@@ -9534,8 +9534,8 @@
       <c r="O179">
         <v>1763</v>
       </c>
-      <c r="P179">
-        <v>15.31</v>
+      <c r="P179" t="str">
+        <v>15.310</v>
       </c>
     </row>
     <row r="180">
@@ -9572,7 +9572,7 @@
       <c r="K180" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L180">
+      <c r="L180" t="str">
         <v>2004</v>
       </c>
       <c r="M180" t="str">
@@ -9584,8 +9584,8 @@
       <c r="O180">
         <v>924</v>
       </c>
-      <c r="P180">
-        <v>9.93</v>
+      <c r="P180" t="str">
+        <v>9.930</v>
       </c>
     </row>
     <row r="181">
@@ -9622,7 +9622,7 @@
       <c r="K181" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L181">
+      <c r="L181" t="str">
         <v>1986</v>
       </c>
       <c r="M181" t="str">
@@ -9634,8 +9634,8 @@
       <c r="O181">
         <v>26600</v>
       </c>
-      <c r="P181">
-        <v>113</v>
+      <c r="P181" t="str">
+        <v>113.000</v>
       </c>
       <c r="Q181" t="str">
         <v>1993 MAN TRUCK WMAF09C338M173408- 1999 HONDA ACCORD SHHCG7520XU001084</v>
@@ -9675,7 +9675,7 @@
       <c r="K182" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L182">
+      <c r="L182" t="str">
         <v>1985</v>
       </c>
       <c r="M182" t="str">
@@ -9687,8 +9687,8 @@
       <c r="O182">
         <v>17520</v>
       </c>
-      <c r="P182">
-        <v>101</v>
+      <c r="P182" t="str">
+        <v>101.000</v>
       </c>
       <c r="Q182" t="str">
         <v>1978 MAN TRUCK 04242287-1980 FIAT TRACTOR 037895</v>
@@ -9728,7 +9728,7 @@
       <c r="K183" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L183">
+      <c r="L183" t="str">
         <v>2025</v>
       </c>
       <c r="M183" t="str">
@@ -9740,8 +9740,8 @@
       <c r="O183">
         <v>2296</v>
       </c>
-      <c r="P183">
-        <v>20.54</v>
+      <c r="P183" t="str">
+        <v>20.540</v>
       </c>
     </row>
     <row r="184">
@@ -9778,7 +9778,7 @@
       <c r="K184" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L184">
+      <c r="L184" t="str">
         <v>2025</v>
       </c>
       <c r="M184" t="str">
@@ -9790,8 +9790,8 @@
       <c r="O184">
         <v>2296</v>
       </c>
-      <c r="P184">
-        <v>20.54</v>
+      <c r="P184" t="str">
+        <v>20.540</v>
       </c>
     </row>
     <row r="185">
@@ -9828,7 +9828,7 @@
       <c r="K185" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L185">
+      <c r="L185" t="str">
         <v>2025</v>
       </c>
       <c r="M185" t="str">
@@ -9840,8 +9840,8 @@
       <c r="O185">
         <v>2077</v>
       </c>
-      <c r="P185">
-        <v>20.41</v>
+      <c r="P185" t="str">
+        <v>20.410</v>
       </c>
     </row>
     <row r="186">
@@ -9878,7 +9878,7 @@
       <c r="K186" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L186">
+      <c r="L186" t="str">
         <v>2025</v>
       </c>
       <c r="M186" t="str">
@@ -9890,8 +9890,8 @@
       <c r="O186">
         <v>2077</v>
       </c>
-      <c r="P186">
-        <v>20.41</v>
+      <c r="P186" t="str">
+        <v>20.410</v>
       </c>
     </row>
     <row r="187">
@@ -9928,7 +9928,7 @@
       <c r="K187" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L187">
+      <c r="L187" t="str">
         <v>2025</v>
       </c>
       <c r="M187" t="str">
@@ -9940,8 +9940,8 @@
       <c r="O187">
         <v>2296</v>
       </c>
-      <c r="P187">
-        <v>20.54</v>
+      <c r="P187" t="str">
+        <v>20.540</v>
       </c>
     </row>
     <row r="188">
@@ -9978,7 +9978,7 @@
       <c r="K188" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L188">
+      <c r="L188" t="str">
         <v>2025</v>
       </c>
       <c r="M188" t="str">
@@ -9990,8 +9990,8 @@
       <c r="O188">
         <v>2077</v>
       </c>
-      <c r="P188">
-        <v>20.41</v>
+      <c r="P188" t="str">
+        <v>20.410</v>
       </c>
     </row>
     <row r="189">
@@ -10028,7 +10028,7 @@
       <c r="K189" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L189">
+      <c r="L189" t="str">
         <v>2025</v>
       </c>
       <c r="M189" t="str">
@@ -10040,8 +10040,8 @@
       <c r="O189">
         <v>2077</v>
       </c>
-      <c r="P189">
-        <v>20.41</v>
+      <c r="P189" t="str">
+        <v>20.410</v>
       </c>
     </row>
     <row r="190">
@@ -10078,7 +10078,7 @@
       <c r="K190" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L190">
+      <c r="L190" t="str">
         <v>2025</v>
       </c>
       <c r="M190" t="str">
@@ -10090,8 +10090,8 @@
       <c r="O190">
         <v>2077</v>
       </c>
-      <c r="P190">
-        <v>20.41</v>
+      <c r="P190" t="str">
+        <v>20.410</v>
       </c>
     </row>
     <row r="191">
@@ -10128,7 +10128,7 @@
       <c r="K191" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L191">
+      <c r="L191" t="str">
         <v>2025</v>
       </c>
       <c r="M191" t="str">
@@ -10140,8 +10140,8 @@
       <c r="O191">
         <v>2296</v>
       </c>
-      <c r="P191">
-        <v>20.54</v>
+      <c r="P191" t="str">
+        <v>20.540</v>
       </c>
     </row>
     <row r="192">
@@ -10178,7 +10178,7 @@
       <c r="K192" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L192">
+      <c r="L192" t="str">
         <v>2025</v>
       </c>
       <c r="M192" t="str">
@@ -10190,8 +10190,8 @@
       <c r="O192">
         <v>2296</v>
       </c>
-      <c r="P192">
-        <v>20.54</v>
+      <c r="P192" t="str">
+        <v>20.540</v>
       </c>
     </row>
     <row r="193">
@@ -10228,7 +10228,7 @@
       <c r="K193" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L193">
+      <c r="L193" t="str">
         <v>2025</v>
       </c>
       <c r="M193" t="str">
@@ -10240,8 +10240,8 @@
       <c r="O193">
         <v>2077</v>
       </c>
-      <c r="P193">
-        <v>20.41</v>
+      <c r="P193" t="str">
+        <v>20.410</v>
       </c>
     </row>
     <row r="194">
@@ -10278,7 +10278,7 @@
       <c r="K194" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L194">
+      <c r="L194" t="str">
         <v>2025</v>
       </c>
       <c r="M194" t="str">
@@ -10290,8 +10290,8 @@
       <c r="O194">
         <v>2296</v>
       </c>
-      <c r="P194">
-        <v>20.54</v>
+      <c r="P194" t="str">
+        <v>20.540</v>
       </c>
     </row>
     <row r="195">
@@ -10328,7 +10328,7 @@
       <c r="K195" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L195">
+      <c r="L195" t="str">
         <v>2011</v>
       </c>
       <c r="M195" t="str">
@@ -10340,8 +10340,8 @@
       <c r="O195">
         <v>12800</v>
       </c>
-      <c r="P195">
-        <v>115.26</v>
+      <c r="P195" t="str">
+        <v>115.260</v>
       </c>
       <c r="Q195" t="str">
         <v>BA 21420253001045 MF 20250068437</v>
@@ -10381,7 +10381,7 @@
       <c r="K196" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L196">
+      <c r="L196" t="str">
         <v>2025</v>
       </c>
       <c r="M196" t="str">
@@ -10393,8 +10393,8 @@
       <c r="O196">
         <v>13500</v>
       </c>
-      <c r="P196">
-        <v>129.54</v>
+      <c r="P196" t="str">
+        <v>129.540</v>
       </c>
       <c r="Q196" t="str">
         <v>TANK SERIAL: 242505104</v>
@@ -10434,7 +10434,7 @@
       <c r="K197" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L197">
+      <c r="L197" t="str">
         <v>2025</v>
       </c>
       <c r="M197" t="str">
@@ -10446,8 +10446,8 @@
       <c r="O197">
         <v>13500</v>
       </c>
-      <c r="P197">
-        <v>129.54</v>
+      <c r="P197" t="str">
+        <v>129.540</v>
       </c>
       <c r="Q197" t="str">
         <v>TANK SERIAL: 242505105</v>
@@ -10487,7 +10487,7 @@
       <c r="K198" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L198">
+      <c r="L198" t="str">
         <v>2025</v>
       </c>
       <c r="M198" t="str">
@@ -10499,8 +10499,8 @@
       <c r="O198">
         <v>13500</v>
       </c>
-      <c r="P198">
-        <v>129.54</v>
+      <c r="P198" t="str">
+        <v>129.540</v>
       </c>
       <c r="Q198" t="str">
         <v>TANK SERIAL: 242505106</v>
@@ -10540,7 +10540,7 @@
       <c r="K199" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L199">
+      <c r="L199" t="str">
         <v>2025</v>
       </c>
       <c r="M199" t="str">
@@ -10552,8 +10552,8 @@
       <c r="O199">
         <v>13500</v>
       </c>
-      <c r="P199">
-        <v>129.54</v>
+      <c r="P199" t="str">
+        <v>129.540</v>
       </c>
       <c r="Q199" t="str">
         <v>TANK SERIAL: 242505107 BA08220253000619/MF20250119669</v>
@@ -10593,7 +10593,7 @@
       <c r="K200" t="str">
         <v>Same As Consignee</v>
       </c>
-      <c r="L200">
+      <c r="L200" t="str">
         <v>2025</v>
       </c>
       <c r="M200" t="str">
@@ -10605,8 +10605,8 @@
       <c r="O200">
         <v>30600</v>
       </c>
-      <c r="P200">
-        <v>200.64</v>
+      <c r="P200" t="str">
+        <v>200.640</v>
       </c>
       <c r="Q200" t="str">
         <v>STC:3 AXLES LOWBED SEMI TRAILER CH:NP83LK29651000483</v>
